--- a/Decks/Narset.xlsx
+++ b/Decks/Narset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17143A22-FB14-4A8B-87C4-F218A7E04314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3256193D-83A1-4758-90D2-43C9DCF5B457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C2AD6E7-26CE-4463-BC0E-991417C1C190}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9C2AD6E7-26CE-4463-BC0E-991417C1C190}"/>
   </bookViews>
   <sheets>
     <sheet name="Narset" sheetId="1" r:id="rId1"/>
@@ -149,9 +149,6 @@
     <t>Fellwar Stone</t>
   </si>
   <si>
-    <t>Tougth Vessel</t>
-  </si>
-  <si>
     <t>Realmbreaker, the Invasion Tree</t>
   </si>
   <si>
@@ -384,6 +381,9 @@
   </si>
   <si>
     <t>Chameleon, Master of Disguise</t>
+  </si>
+  <si>
+    <t>Thought Vessel</t>
   </si>
 </sst>
 </file>
@@ -1456,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="D44" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="F44"/>
     </row>
@@ -1472,869 +1472,869 @@
         <v>1</v>
       </c>
       <c r="C45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" t="s">
         <v>38</v>
-      </c>
-      <c r="D45" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="D46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F48"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" t="s">
         <v>46</v>
-      </c>
-      <c r="D51" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F54"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F55"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C56" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" t="s">
         <v>53</v>
-      </c>
-      <c r="D56" t="s">
-        <v>54</v>
       </c>
       <c r="F56"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C57" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" t="s">
         <v>55</v>
-      </c>
-      <c r="D57" t="s">
-        <v>56</v>
       </c>
       <c r="F57"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" t="s">
         <v>57</v>
-      </c>
-      <c r="D58" t="s">
-        <v>58</v>
       </c>
       <c r="F58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="D60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F61"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F62"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F63"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F64"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C65" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D65" t="s">
         <v>66</v>
-      </c>
-      <c r="D65" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C71" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D71" t="s">
         <v>73</v>
-      </c>
-      <c r="D71" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D72" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="D73" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F75"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="D78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82" s="5" t="b">
         <f>C82&lt;&gt;D82</f>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="D85" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="D90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C93" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D93" t="s">
         <v>100</v>
-      </c>
-      <c r="D93" t="s">
-        <v>101</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C94" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D94" t="s">
         <v>102</v>
-      </c>
-      <c r="D94" t="s">
-        <v>103</v>
       </c>
       <c r="F94"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D95" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F95"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D96" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D97" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="D98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C99" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D99" t="s">
         <v>109</v>
-      </c>
-      <c r="D99" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Narset.xlsx
+++ b/Decks/Narset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3256193D-83A1-4758-90D2-43C9DCF5B457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B1D8BD-CA78-408C-86C3-84660B9927EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9C2AD6E7-26CE-4463-BC0E-991417C1C190}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C2AD6E7-26CE-4463-BC0E-991417C1C190}"/>
   </bookViews>
   <sheets>
     <sheet name="Narset" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="115">
   <si>
     <t>Função</t>
   </si>
@@ -300,9 +300,6 @@
   </si>
   <si>
     <t>Trailblazer's Boots</t>
-  </si>
-  <si>
-    <t>Enterprising Scallywag</t>
   </si>
   <si>
     <t>Remoção</t>
@@ -792,7 +789,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="41.140625" customWidth="1"/>
     <col min="6" max="6" width="41.140625" style="7" customWidth="1"/>
   </cols>
@@ -1456,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F44"/>
     </row>
@@ -1965,10 +1962,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>80</v>
@@ -2043,10 +2040,10 @@
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D82" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2070,271 +2067,271 @@
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D84" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="D85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D90" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C93" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D93" t="s">
         <v>99</v>
-      </c>
-      <c r="D93" t="s">
-        <v>100</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C94" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D94" t="s">
         <v>101</v>
-      </c>
-      <c r="D94" t="s">
-        <v>102</v>
       </c>
       <c r="F94"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D95" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F95"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D97" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C99" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D99" t="s">
         <v>108</v>
-      </c>
-      <c r="D99" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D101" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Narset.xlsx
+++ b/Decks/Narset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B1D8BD-CA78-408C-86C3-84660B9927EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A4FA98-D158-443A-8996-C29401338795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C2AD6E7-26CE-4463-BC0E-991417C1C190}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="118">
   <si>
     <t>Função</t>
   </si>
@@ -170,18 +170,12 @@
     <t>Shorikai, Genesis Engine</t>
   </si>
   <si>
-    <t>Whirlwind of Thought</t>
-  </si>
-  <si>
     <t>Crashing Drawbridge</t>
   </si>
   <si>
     <t>Brass's Tunnel-Grinder</t>
   </si>
   <si>
-    <t>Spirit Water Revival</t>
-  </si>
-  <si>
     <t>Mirrodin Besieged</t>
   </si>
   <si>
@@ -206,9 +200,6 @@
     <t>Khorvath's Fury</t>
   </si>
   <si>
-    <t>Cut your Losses</t>
-  </si>
-  <si>
     <t>Reforge the Soul</t>
   </si>
   <si>
@@ -257,9 +248,6 @@
     <t>Surge of Salvation</t>
   </si>
   <si>
-    <t>Maddening Cacophony</t>
-  </si>
-  <si>
     <t>The Mindskinner</t>
   </si>
   <si>
@@ -359,9 +347,6 @@
     <t>Full Throttle</t>
   </si>
   <si>
-    <t>Traumatize</t>
-  </si>
-  <si>
     <t>World at War</t>
   </si>
   <si>
@@ -381,6 +366,30 @@
   </si>
   <si>
     <t>Thought Vessel</t>
+  </si>
+  <si>
+    <t>Prismatic Lens</t>
+  </si>
+  <si>
+    <t>Cosmic Cube</t>
+  </si>
+  <si>
+    <t>Surveillance Room</t>
+  </si>
+  <si>
+    <t>Doom's Time Platform</t>
+  </si>
+  <si>
+    <t>Multiversal Recruitment</t>
+  </si>
+  <si>
+    <t>Wanda's Vision</t>
+  </si>
+  <si>
+    <t>Wedding Ring</t>
+  </si>
+  <si>
+    <t>Namor, Atlantean King</t>
   </si>
 </sst>
 </file>
@@ -834,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B65" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -1104,14 +1113,14 @@
         <v>8</v>
       </c>
       <c r="B21" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C21&lt;&gt;D21</f>
         <v>0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1273,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1284,7 +1293,7 @@
         <v>8</v>
       </c>
       <c r="B33" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C33&lt;&gt;D33</f>
         <v>0</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -1453,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F44"/>
     </row>
@@ -1465,29 +1474,29 @@
         <v>30</v>
       </c>
       <c r="B45" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>C45&lt;&gt;D45</f>
+        <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1499,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1514,12 +1523,11 @@
         <v>0</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D48" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -1530,11 +1538,12 @@
         <v>0</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D49" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F49"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -1545,10 +1554,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1557,13 +1566,13 @@
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1572,13 +1581,13 @@
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1590,47 +1599,47 @@
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D53" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F54"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>47</v>
+      </c>
+      <c r="B55" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F55"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1646,231 +1655,230 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C57" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" t="s">
         <v>54</v>
-      </c>
-      <c r="D57" t="s">
-        <v>55</v>
       </c>
       <c r="F57"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D58" t="s">
-        <v>57</v>
-      </c>
-      <c r="F58"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F59"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D60" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F60"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B61" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="D61" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D62" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F62"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F63"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D64" t="s">
-        <v>64</v>
-      </c>
-      <c r="F64"/>
+        <v>63</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D65" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D66" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D67" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D68" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D71" t="s">
         <v>73</v>
@@ -1878,460 +1886,463 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D72" t="s">
         <v>74</v>
       </c>
+      <c r="F72"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B73" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C73&lt;&gt;D73</f>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="D73" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>71</v>
+      </c>
+      <c r="B74" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B74" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="D74" t="s">
-        <v>77</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D75" t="s">
-        <v>78</v>
-      </c>
-      <c r="F75"/>
+        <v>107</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D76" t="s">
-        <v>79</v>
-      </c>
-      <c r="F76"/>
+        <v>78</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D77" t="s">
-        <v>112</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B78" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C78&lt;&gt;D78</f>
+        <v>1</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D78" t="s">
-        <v>82</v>
+        <v>111</v>
+      </c>
+      <c r="F78" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B79" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C79&lt;&gt;D79</f>
+        <v>1</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D80" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B81" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C81&lt;&gt;D81</f>
+        <v>1</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D81" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B82" s="5" t="b">
         <f>C82&lt;&gt;D82</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D82" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>77</v>
+      </c>
+      <c r="B83" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C83" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="D83" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B84" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C84&lt;&gt;D84</f>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D84" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D85" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D86" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D87" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D88" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D89" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D90" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D91" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D93" t="s">
-        <v>99</v>
-      </c>
-      <c r="F93"/>
+        <v>92</v>
+      </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D94" t="s">
-        <v>101</v>
-      </c>
-      <c r="F94"/>
+        <v>93</v>
+      </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>90</v>
+      </c>
+      <c r="B95" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="D95" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F95"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D96" t="s">
+        <v>97</v>
+      </c>
+      <c r="F96"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>90</v>
+      </c>
+      <c r="B97" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D97" t="s">
+        <v>98</v>
+      </c>
+      <c r="F97"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>90</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D98" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>90</v>
+      </c>
+      <c r="B99" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D100" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+      <c r="B101" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D101" t="s">
         <v>103</v>
-      </c>
-      <c r="D96" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>94</v>
-      </c>
-      <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D97" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>105</v>
-      </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D98" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>105</v>
-      </c>
-      <c r="B99" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D99" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>105</v>
-      </c>
-      <c r="B100" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D100" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>105</v>
-      </c>
-      <c r="B101" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D101" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Narset.xlsx
+++ b/Decks/Narset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A4FA98-D158-443A-8996-C29401338795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B8BBE3-2DC2-47E9-8B75-A265C7123972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C2AD6E7-26CE-4463-BC0E-991417C1C190}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="117">
   <si>
     <t>Função</t>
   </si>
@@ -197,9 +197,6 @@
     <t>Opt</t>
   </si>
   <si>
-    <t>Khorvath's Fury</t>
-  </si>
-  <si>
     <t>Reforge the Soul</t>
   </si>
   <si>
@@ -326,9 +323,6 @@
     <t>Ghostly Prison</t>
   </si>
   <si>
-    <t>Sanctum of Calm Waters</t>
-  </si>
-  <si>
     <t>Slash the Ranks</t>
   </si>
   <si>
@@ -341,15 +335,9 @@
     <t>Sculpted Sunburst</t>
   </si>
   <si>
-    <t>Combate</t>
-  </si>
-  <si>
     <t>Full Throttle</t>
   </si>
   <si>
-    <t>World at War</t>
-  </si>
-  <si>
     <t>Relentless Assault</t>
   </si>
   <si>
@@ -390,6 +378,15 @@
   </si>
   <si>
     <t>Namor, Atlantean King</t>
+  </si>
+  <si>
+    <t>Irma, Part-Time Mutant</t>
+  </si>
+  <si>
+    <t>Hulkling, Young Avenger</t>
+  </si>
+  <si>
+    <t>Gogo, Mysterious Mime</t>
   </si>
 </sst>
 </file>
@@ -843,7 +840,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B65" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B64" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -1117,10 +1114,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1462,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F44"/>
     </row>
@@ -1478,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1569,10 +1566,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D51" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1646,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
         <v>53</v>
@@ -1659,34 +1656,34 @@
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D57" t="s">
         <v>54</v>
       </c>
-      <c r="F57"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D58" t="s">
-        <v>55</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1702,7 +1699,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1718,7 +1715,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1734,7 +1731,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1750,23 +1747,22 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D63" t="s">
-        <v>61</v>
-      </c>
-      <c r="F63"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1781,10 +1777,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B65" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B65:B101" si="1">C65&lt;&gt;D65</f>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -1796,10 +1792,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -1811,7 +1807,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1826,7 +1822,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1841,117 +1837,117 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D69" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D70" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D71" t="s">
         <v>73</v>
       </c>
+      <c r="F71"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>C72&lt;&gt;D72</f>
+        <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D72" t="s">
-        <v>74</v>
-      </c>
-      <c r="F72"/>
+        <v>113</v>
+      </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B73" s="5" t="b">
-        <f>C73&lt;&gt;D73</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="D73" t="s">
-        <v>117</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D74" t="s">
+        <v>103</v>
+      </c>
+      <c r="F74" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D74" t="s">
-        <v>75</v>
-      </c>
-      <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="D75" t="s">
-        <v>107</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1966,383 +1962,384 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C77&lt;&gt;D77</f>
+        <v>1</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D77" t="s">
-        <v>79</v>
+        <v>107</v>
+      </c>
+      <c r="F77" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B78" s="5" t="b">
         <f>C78&lt;&gt;D78</f>
         <v>1</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D78" t="s">
-        <v>111</v>
-      </c>
-      <c r="F78" t="s">
-        <v>51</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="F78"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B79" s="5" t="b">
         <f>C79&lt;&gt;D79</f>
         <v>1</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D79" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D80" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B81" s="5" t="b">
         <f>C81&lt;&gt;D81</f>
         <v>1</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B82" s="5" t="b">
         <f>C82&lt;&gt;D82</f>
         <v>1</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D83" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B84" s="5" t="b">
         <f>C84&lt;&gt;D84</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D84" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C85&lt;&gt;D85</f>
+        <v>1</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D85" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B86" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C86&lt;&gt;D86</f>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D86" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>76</v>
+      </c>
+      <c r="B87" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D87" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>76</v>
+      </c>
+      <c r="B88" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D88" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>83</v>
+      </c>
+      <c r="B89" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C89" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B87" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C87" s="6" t="s">
+      <c r="D89" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D90" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>84</v>
-      </c>
-      <c r="B88" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C88" s="6" t="s">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>83</v>
+      </c>
+      <c r="B91" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C91" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D91" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>84</v>
-      </c>
-      <c r="B89" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C89" s="6" t="s">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>83</v>
+      </c>
+      <c r="B92" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D92" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>84</v>
-      </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="6" t="s">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>83</v>
+      </c>
+      <c r="B93" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D93" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>84</v>
-      </c>
-      <c r="B91" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C91" s="6" t="s">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>89</v>
       </c>
-      <c r="D91" t="s">
+      <c r="B94" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D94" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>90</v>
-      </c>
-      <c r="B92" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C92" s="6" t="s">
+      <c r="B95" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D95" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>90</v>
-      </c>
-      <c r="B93" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C93" s="6" t="s">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>89</v>
+      </c>
+      <c r="B96" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D96" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>90</v>
-      </c>
-      <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>90</v>
-      </c>
-      <c r="B95" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D95" t="s">
-        <v>95</v>
-      </c>
-      <c r="F95"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>90</v>
-      </c>
-      <c r="B96" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D96" t="s">
-        <v>97</v>
-      </c>
-      <c r="F96"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D97" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F97"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D98" t="s">
-        <v>99</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D99" t="s">
-        <v>100</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F99"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D100" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D101" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
